--- a/Data/FlightPlan/FPL_27AUG26.xlsx
+++ b/Data/FlightPlan/FPL_27AUG26.xlsx
@@ -605,6 +605,12 @@
     <t>11:00</t>
   </si>
   <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
     <t>13:20</t>
   </si>
   <si>
@@ -635,9 +641,6 @@
     <t>VN-A553</t>
   </si>
   <si>
-    <t>12:00</t>
-  </si>
-  <si>
     <t>12:30</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
     <t>VN-A578</t>
   </si>
   <si>
+    <t>08:20</t>
+  </si>
+  <si>
     <t>17:15</t>
   </si>
   <si>
@@ -740,9 +746,6 @@
     <t>12:45</t>
   </si>
   <si>
-    <t>13:50</t>
-  </si>
-  <si>
     <t>PXU</t>
   </si>
   <si>
@@ -947,9 +950,6 @@
     <t>06:40</t>
   </si>
   <si>
-    <t>08:20</t>
-  </si>
-  <si>
     <t>14:45</t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Total Record(s): 397</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 26, 2026 21:41</t>
+    <t xml:space="preserve">Generated on  Aug 27, 2026 00:55</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5552,11 +5552,11 @@
         <v>196</v>
       </c>
       <c t="s" r="K132" s="7">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>135</v>
+        <v>197</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -5588,9 +5588,13 @@
       <c t="s" r="J133" s="7">
         <v>44</v>
       </c>
-      <c r="K133" s="7"/>
+      <c t="s" r="K133" s="7">
+        <v>198</v>
+      </c>
       <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
+      <c t="s" r="M133" s="7">
+        <v>199</v>
+      </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c t="s" r="A134" s="6">
@@ -5616,14 +5620,18 @@
         <v>78</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>199</v>
-      </c>
-      <c r="K134" s="7"/>
+        <v>201</v>
+      </c>
+      <c t="s" r="K134" s="7">
+        <v>58</v>
+      </c>
       <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
+      <c t="s" r="M134" s="7">
+        <v>70</v>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c t="s" r="A135" s="6">
@@ -5652,7 +5660,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5685,7 +5693,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5697,7 +5705,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>101</v>
@@ -5718,7 +5726,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5727,13 +5735,13 @@
         <v>78</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5751,13 +5759,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>78</v>
@@ -5784,7 +5792,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5796,10 +5804,10 @@
         <v>115</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5832,7 +5840,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5847,7 +5855,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5865,7 +5873,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5877,7 +5885,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>46</v>
@@ -5898,7 +5906,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5910,7 +5918,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>85</v>
@@ -5931,7 +5939,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5943,7 +5951,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>144</v>
@@ -5964,7 +5972,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5973,7 +5981,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I146" s="7">
         <v>39</v>
@@ -5997,22 +6005,22 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6045,7 +6053,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6054,10 +6062,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>157</v>
@@ -6078,13 +6086,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
@@ -6111,7 +6119,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6144,7 +6152,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6177,7 +6185,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6189,7 +6197,7 @@
         <v>141</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>179</v>
@@ -6225,13 +6233,13 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>17</v>
@@ -6258,7 +6266,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6291,7 +6299,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6306,7 +6314,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6324,7 +6332,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6333,13 +6341,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6372,7 +6380,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6389,9 +6397,13 @@
       <c t="s" r="J160" s="7">
         <v>179</v>
       </c>
-      <c r="K160" s="7"/>
+      <c t="s" r="K160" s="7">
+        <v>226</v>
+      </c>
       <c r="L160" s="7"/>
-      <c r="M160" s="7"/>
+      <c t="s" r="M160" s="7">
+        <v>197</v>
+      </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c t="s" r="A161" s="6">
@@ -6405,7 +6417,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6417,7 +6429,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>70</v>
@@ -6438,7 +6450,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6450,7 +6462,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>60</v>
@@ -6471,7 +6483,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6483,10 +6495,10 @@
         <v>141</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6519,19 +6531,19 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>172</v>
@@ -6552,7 +6564,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6564,10 +6576,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6600,7 +6612,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6612,7 +6624,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>34</v>
@@ -6633,7 +6645,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6645,7 +6657,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>60</v>
@@ -6666,7 +6678,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6681,7 +6693,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6714,7 +6726,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6726,7 +6738,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>65</v>
@@ -6747,7 +6759,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6762,7 +6774,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6780,7 +6792,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6789,13 +6801,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6813,22 +6825,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
+        <v>239</v>
+      </c>
+      <c r="F175" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G175" s="8">
+        <v>242</v>
+      </c>
+      <c t="s" r="H175" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I175" s="7">
+        <v>199</v>
+      </c>
+      <c t="s" r="J175" s="7">
         <v>237</v>
-      </c>
-      <c r="F175" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G175" s="8">
-        <v>240</v>
-      </c>
-      <c t="s" r="H175" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I175" s="7">
-        <v>243</v>
-      </c>
-      <c t="s" r="J175" s="7">
-        <v>235</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6846,7 +6858,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6855,7 +6867,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>47</v>
@@ -6879,19 +6891,19 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>38</v>
@@ -6912,7 +6924,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6921,13 +6933,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6945,22 +6957,22 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6993,7 +7005,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7026,7 +7038,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7059,7 +7071,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7068,7 +7080,7 @@
         <v>71</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>164</v>
@@ -7092,22 +7104,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7125,7 +7137,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7134,13 +7146,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7158,19 +7170,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>106</v>
@@ -7206,7 +7218,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7215,13 +7227,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I188" s="7">
         <v>155</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7239,13 +7251,13 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>16</v>
@@ -7254,7 +7266,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7272,7 +7284,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7287,7 +7299,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7320,7 +7332,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7335,7 +7347,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7353,7 +7365,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7362,13 +7374,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7386,13 +7398,13 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>17</v>
@@ -7419,7 +7431,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7431,7 +7443,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>19</v>
@@ -7467,7 +7479,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7476,10 +7488,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>117</v>
@@ -7500,13 +7512,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>17</v>
@@ -7533,7 +7545,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7542,10 +7554,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>164</v>
@@ -7566,19 +7578,19 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>46</v>
@@ -7599,7 +7611,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7611,7 +7623,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>127</v>
@@ -7632,7 +7644,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7644,10 +7656,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7680,7 +7692,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7695,7 +7707,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7713,7 +7725,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7746,7 +7758,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7755,13 +7767,13 @@
         <v>133</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7779,19 +7791,19 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>133</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>35</v>
@@ -7812,7 +7824,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7860,7 +7872,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7893,7 +7905,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7908,7 +7920,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7926,7 +7938,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7941,7 +7953,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7959,7 +7971,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7971,7 +7983,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>152</v>
@@ -7992,7 +8004,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8025,7 +8037,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8037,7 +8049,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>106</v>
@@ -8058,7 +8070,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8106,7 +8118,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8139,7 +8151,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8172,7 +8184,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8184,7 +8196,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>94</v>
@@ -8205,7 +8217,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8238,7 +8250,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8250,10 +8262,10 @@
         <v>78</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8271,7 +8283,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8283,7 +8295,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>193</v>
@@ -8319,7 +8331,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8328,10 +8340,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>89</v>
@@ -8352,19 +8364,19 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>55</v>
@@ -8385,22 +8397,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8418,7 +8430,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8427,13 +8439,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8451,13 +8463,13 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>16</v>
@@ -8484,7 +8496,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8496,7 +8508,7 @@
         <v>158</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>26</v>
@@ -8517,7 +8529,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8529,10 +8541,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8565,7 +8577,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8574,13 +8586,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8598,13 +8610,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>16</v>
@@ -8613,7 +8625,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8631,7 +8643,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8640,10 +8652,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>188</v>
@@ -8664,13 +8676,13 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>16</v>
@@ -8712,7 +8724,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8724,10 +8736,10 @@
         <v>158</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8745,7 +8757,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8778,7 +8790,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8787,13 +8799,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I240" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8811,13 +8823,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
@@ -8826,7 +8838,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8844,7 +8856,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8892,7 +8904,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8907,7 +8919,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8925,7 +8937,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8937,7 +8949,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>58</v>
@@ -8958,7 +8970,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -8967,10 +8979,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>103</v>
@@ -8991,13 +9003,13 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>17</v>
@@ -9006,7 +9018,7 @@
         <v>188</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9024,7 +9036,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9039,7 +9051,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9072,7 +9084,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9087,7 +9099,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9105,7 +9117,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9117,7 +9129,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>157</v>
@@ -9138,7 +9150,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9147,7 +9159,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>187</v>
@@ -9171,13 +9183,13 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>16</v>
@@ -9186,7 +9198,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9204,7 +9216,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9213,13 +9225,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9237,13 +9249,13 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>16</v>
@@ -9252,7 +9264,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9270,7 +9282,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9282,7 +9294,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>18</v>
@@ -9318,7 +9330,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9330,10 +9342,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9351,7 +9363,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9360,7 +9372,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>118</v>
@@ -9384,13 +9396,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>17</v>
@@ -9399,7 +9411,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9417,7 +9429,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9429,7 +9441,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>96</v>
@@ -9450,7 +9462,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9465,7 +9477,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9498,13 +9510,13 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>16</v>
@@ -9513,7 +9525,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9531,7 +9543,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9540,10 +9552,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>137</v>
@@ -9564,19 +9576,19 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>138</v>
@@ -9597,7 +9609,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9645,7 +9657,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9654,13 +9666,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9678,13 +9690,13 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>71</v>
@@ -9693,7 +9705,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9711,7 +9723,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9744,7 +9756,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9777,7 +9789,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9825,7 +9837,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9834,10 +9846,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>52</v>
@@ -9862,25 +9874,25 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>312</v>
+        <v>226</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>55</v>
       </c>
       <c t="s" r="K276" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
@@ -9899,19 +9911,19 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
+        <v>311</v>
+      </c>
+      <c r="F277" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G277" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H277" s="8">
+        <v>242</v>
+      </c>
+      <c t="s" r="I277" s="7">
         <v>310</v>
-      </c>
-      <c r="F277" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G277" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H277" s="8">
-        <v>240</v>
-      </c>
-      <c t="s" r="I277" s="7">
-        <v>309</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>313</v>
@@ -9932,13 +9944,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>16</v>
@@ -9947,7 +9959,7 @@
         <v>143</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9965,7 +9977,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -9974,7 +9986,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>59</v>
@@ -9998,13 +10010,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>16</v>
@@ -10031,7 +10043,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10064,7 +10076,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10157,7 +10169,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>118</v>
@@ -10190,7 +10202,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>102</v>
@@ -10259,7 +10271,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10373,7 +10385,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10403,7 +10415,7 @@
         <v>116</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>165</v>
@@ -10439,7 +10451,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10661,7 +10673,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>19</v>
@@ -10670,7 +10682,7 @@
         <v>108</v>
       </c>
       <c t="s" r="K302" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
@@ -10695,7 +10707,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>17</v>
@@ -10707,7 +10719,7 @@
         <v>99</v>
       </c>
       <c t="s" r="K303" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
@@ -10738,13 +10750,13 @@
         <v>116</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>165</v>
       </c>
       <c t="s" r="K304" s="7">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
@@ -10809,13 +10821,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>188</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10839,7 +10851,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>17</v>
@@ -10893,7 +10905,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>156</v>
@@ -10995,7 +11007,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11025,7 +11037,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>92</v>
@@ -11058,7 +11070,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>35</v>
@@ -11106,7 +11118,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>335</v>
@@ -11139,7 +11151,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>126</v>
@@ -11169,13 +11181,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>336</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11199,16 +11211,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11235,7 +11247,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>337</v>
@@ -11265,7 +11277,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>16</v>
@@ -11322,7 +11334,7 @@
         <v>340</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11355,7 +11367,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11388,7 +11400,7 @@
         <v>341</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11421,7 +11433,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11469,7 +11481,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11499,7 +11511,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>151</v>
@@ -11535,7 +11547,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11568,7 +11580,7 @@
         <v>343</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11748,7 +11760,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11775,10 +11787,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>47</v>
@@ -11805,7 +11817,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>17</v>
@@ -11841,10 +11853,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>349</v>
@@ -11871,7 +11883,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>17</v>
@@ -11961,7 +11973,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11991,7 +12003,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>90</v>
@@ -12168,13 +12180,13 @@
         <v>133</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12198,7 +12210,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>133</v>
@@ -12237,7 +12249,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>343</v>
@@ -12273,7 +12285,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12351,7 +12363,7 @@
         <v>318</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>195</v>
@@ -12387,7 +12399,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>312</v>
+        <v>226</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12420,7 +12432,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12486,7 +12498,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12546,7 +12558,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>103</v>
@@ -12576,13 +12588,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>349</v>
@@ -12633,7 +12645,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12666,7 +12678,7 @@
         <v>359</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12696,7 +12708,7 @@
         <v>318</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>152</v>
@@ -12762,10 +12774,10 @@
         <v>133</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12840,13 +12852,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12870,10 +12882,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>363</v>
@@ -12903,7 +12915,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>16</v>
@@ -12978,7 +12990,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13008,7 +13020,7 @@
         <v>116</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>152</v>
@@ -13041,7 +13053,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>360</v>
@@ -13092,7 +13104,7 @@
         <v>365</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13158,7 +13170,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13191,7 +13203,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13221,10 +13233,10 @@
         <v>355</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13320,7 +13332,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>366</v>
@@ -13365,13 +13377,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13395,7 +13407,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
@@ -13431,7 +13443,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>109</v>
@@ -13461,13 +13473,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>103</v>
@@ -13533,7 +13545,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>18</v>
@@ -13581,7 +13593,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>100</v>
@@ -13614,7 +13626,7 @@
         <v>318</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>370</v>
@@ -13716,7 +13728,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13761,7 +13773,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>23</v>
@@ -13791,7 +13803,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I404" s="7">
         <v>143</v>
@@ -13821,7 +13833,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>17</v>
@@ -13908,7 +13920,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>352</v>
@@ -13938,7 +13950,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>187</v>
@@ -13968,16 +13980,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14007,10 +14019,10 @@
         <v>318</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14070,13 +14082,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>180</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14100,7 +14112,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>17</v>
@@ -14157,7 +14169,7 @@
         <v>196</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14253,7 +14265,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>378</v>
@@ -14415,10 +14427,10 @@
         <v>88</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14481,7 +14493,7 @@
         <v>173</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>382</v>
@@ -14565,7 +14577,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14727,7 +14739,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>73</v>
@@ -14757,7 +14769,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I436" s="7">
         <v>314</v>
@@ -14787,7 +14799,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>17</v>
@@ -14844,7 +14856,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14877,7 +14889,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14910,7 +14922,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -14943,7 +14955,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15039,7 +15051,7 @@
         <v>368</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J445" s="7">
         <v>316</v>
@@ -15117,10 +15129,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>46</v>
@@ -15147,7 +15159,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="H449" s="8">
         <v>16</v>
@@ -15222,7 +15234,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15267,7 +15279,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J453" s="7">
         <v>65</v>
@@ -15303,7 +15315,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15333,7 +15345,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>165</v>
@@ -15369,7 +15381,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15411,7 +15423,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I458" s="7">
         <v>156</v>
@@ -15441,10 +15453,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I459" s="7">
         <v>35</v>
@@ -15474,10 +15486,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I460" s="7">
         <v>60</v>
@@ -15507,7 +15519,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>17</v>
@@ -15561,7 +15573,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J463" s="7">
         <v>197</v>
@@ -15594,7 +15606,7 @@
         <v>395</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J464" s="7">
         <v>344</v>
@@ -15630,7 +15642,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
@@ -15675,7 +15687,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J467" s="7">
         <v>356</v>
@@ -15708,7 +15720,7 @@
         <v>397</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J468" s="7">
         <v>363</v>
@@ -15759,7 +15771,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -16069,7 +16081,7 @@
         <v>408</v>
       </c>
       <c t="s" r="I481" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J481" s="7">
         <v>74</v>

--- a/Data/FlightPlan/FPL_27AUG26.xlsx
+++ b/Data/FlightPlan/FPL_27AUG26.xlsx
@@ -143,6 +143,42 @@
     <t>12:35</t>
   </si>
   <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
     <t>14:05</t>
   </si>
   <si>
@@ -164,25 +200,31 @@
     <t>22:50</t>
   </si>
   <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>13:05</t>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>14:02</t>
   </si>
   <si>
     <t>TPE</t>
@@ -194,51 +236,15 @@
     <t>18:00</t>
   </si>
   <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
     <t>20:55</t>
   </si>
   <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>14:02</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
     <t>PUS</t>
   </si>
   <si>
@@ -338,9 +344,6 @@
     <t>12:40</t>
   </si>
   <si>
-    <t>14:50</t>
-  </si>
-  <si>
     <t>14:29</t>
   </si>
   <si>
@@ -350,9 +353,6 @@
     <t>16:25</t>
   </si>
   <si>
-    <t>18:25</t>
-  </si>
-  <si>
     <t>19:10</t>
   </si>
   <si>
@@ -899,576 +899,579 @@
     <t>12:15</t>
   </si>
   <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:37</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>13:52</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:17</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>13:23</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>14:26</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>06:54</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:27</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>14:18</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>09:12</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>06:53</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>09:09</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>12:36</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:22</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>06:29</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:13</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>12:26</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:38</t>
+  </si>
+  <si>
+    <t>08:23</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:41</t>
+  </si>
+  <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>12:52</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>15:27</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>07:33</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
     <t>15:14</t>
   </si>
   <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:37</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>13:52</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>09:58</t>
-  </si>
-  <si>
-    <t>12:17</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>10:42</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>14:01</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:17</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:34</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>12:02</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>13:23</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>11:42</t>
-  </si>
-  <si>
-    <t>13:28</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>14:26</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>06:54</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:27</t>
-  </si>
-  <si>
-    <t>12:57</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>13:16</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:27</t>
-  </si>
-  <si>
-    <t>11:21</t>
-  </si>
-  <si>
-    <t>14:18</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>12:04</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>09:12</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:23</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>06:53</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>08:42</t>
-  </si>
-  <si>
-    <t>12:13</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>10:13</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>10:04</t>
-  </si>
-  <si>
-    <t>11:58</t>
-  </si>
-  <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>09:09</t>
-  </si>
-  <si>
-    <t>10:39</t>
-  </si>
-  <si>
-    <t>12:36</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>09:22</t>
-  </si>
-  <si>
-    <t>12:24</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>06:29</t>
-  </si>
-  <si>
-    <t>08:14</t>
-  </si>
-  <si>
-    <t>12:16</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:13</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>06:39</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:38</t>
-  </si>
-  <si>
-    <t>10:11</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:38</t>
-  </si>
-  <si>
-    <t>08:23</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>11:22</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>13:47</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:41</t>
-  </si>
-  <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>12:52</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>15:27</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>08:54</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>07:33</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
     <t>03:55</t>
   </si>
   <si>
@@ -1559,7 +1562,7 @@
     <t>Total Record(s): 397</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 27, 2026 12:53</t>
+    <t xml:space="preserve">Generated on  Aug 27, 2026 13:02</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2413,7 +2416,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="7">
-        <v>143</v>
+        <v>467</v>
       </c>
       <c t="s" r="C17" s="7">
         <v>14</v>
@@ -2429,13 +2432,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H17" s="8">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c t="s" r="I17" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="J17" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -2446,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="7">
-        <v>146</v>
+        <v>468</v>
       </c>
       <c t="s" r="C18" s="7">
         <v>14</v>
@@ -2459,16 +2462,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G18" s="8">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c t="s" r="H18" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I18" s="7">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c t="s" r="J18" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2476,10 +2479,10 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c t="s" r="A19" s="6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B19" s="7">
-        <v>523</v>
+        <v>938</v>
       </c>
       <c t="s" r="C19" s="7">
         <v>14</v>
@@ -2495,95 +2498,97 @@
         <v>17</v>
       </c>
       <c t="s" r="H19" s="8">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c t="s" r="A20" s="6">
-        <v>13</v>
-      </c>
-      <c r="B20" s="7">
-        <v>526</v>
-      </c>
-      <c t="s" r="C20" s="7">
-        <v>14</v>
-      </c>
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c t="s" r="E20" s="7">
-        <v>39</v>
-      </c>
-      <c r="F20" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G20" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H20" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I20" s="7">
-        <v>49</v>
-      </c>
-      <c t="s" r="J20" s="7">
-        <v>50</v>
-      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c t="s" r="A21" s="6">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B21" s="7">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c t="s" r="C21" s="7">
         <v>14</v>
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G21" s="8">
+        <v>53</v>
+      </c>
+      <c t="s" r="H21" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H21" s="8">
-        <v>51</v>
-      </c>
       <c t="s" r="I21" s="7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c t="s" r="J21" s="7">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
+      <c t="s" r="M21" s="7">
+        <v>30</v>
+      </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+      <c t="s" r="A22" s="6">
+        <v>13</v>
+      </c>
+      <c r="B22" s="7">
+        <v>143</v>
+      </c>
+      <c t="s" r="C22" s="7">
+        <v>14</v>
+      </c>
       <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
+      <c t="s" r="E22" s="7">
+        <v>52</v>
+      </c>
+      <c r="F22" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G22" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H22" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I22" s="7">
+        <v>56</v>
+      </c>
+      <c t="s" r="J22" s="7">
+        <v>57</v>
+      </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
@@ -2593,49 +2598,47 @@
         <v>13</v>
       </c>
       <c r="B23" s="7">
-        <v>933</v>
+        <v>146</v>
       </c>
       <c t="s" r="C23" s="7">
         <v>14</v>
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G23" s="8">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c t="s" r="H23" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-      <c t="s" r="M23" s="7">
-        <v>30</v>
-      </c>
+      <c r="M23" s="7"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c t="s" r="A24" s="6">
         <v>13</v>
       </c>
       <c r="B24" s="7">
-        <v>942</v>
+        <v>523</v>
       </c>
       <c t="s" r="C24" s="7">
         <v>14</v>
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
@@ -2644,10 +2647,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H24" s="8">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c t="s" r="J24" s="7">
         <v>60</v>
@@ -2661,29 +2664,29 @@
         <v>13</v>
       </c>
       <c r="B25" s="7">
-        <v>943</v>
+        <v>526</v>
       </c>
       <c t="s" r="C25" s="7">
         <v>14</v>
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G25" s="8">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="H25" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2701,7 +2704,7 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
@@ -2710,13 +2713,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H26" s="8">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2749,7 +2752,7 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
@@ -2761,15 +2764,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
       <c t="s" r="M28" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -2784,7 +2787,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2796,15 +2799,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
       <c t="s" r="M29" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
@@ -2812,14 +2815,14 @@
         <v>13</v>
       </c>
       <c r="B30" s="7">
-        <v>467</v>
+        <v>942</v>
       </c>
       <c t="s" r="C30" s="7">
         <v>14</v>
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2828,46 +2831,50 @@
         <v>17</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>73</v>
-      </c>
-      <c r="K30" s="7"/>
+        <v>74</v>
+      </c>
+      <c t="s" r="K30" s="7">
+        <v>75</v>
+      </c>
       <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
+      <c t="s" r="M30" s="7">
+        <v>76</v>
+      </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c t="s" r="A31" s="6">
         <v>13</v>
       </c>
       <c r="B31" s="7">
-        <v>468</v>
+        <v>943</v>
       </c>
       <c t="s" r="C31" s="7">
         <v>14</v>
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="H31" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2885,7 +2892,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2894,10 +2901,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H32" s="8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c t="s" r="J32" s="7">
         <v>19</v>
@@ -2929,11 +2936,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C34" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2942,18 +2949,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H34" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c t="s" r="M34" s="7">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2968,29 +2975,29 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G35" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H35" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c t="s" r="K35" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L35" s="7"/>
       <c t="s" r="M35" s="7">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -3020,7 +3027,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -3029,18 +3036,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c t="s" r="I37" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c t="s" r="M37" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -3055,22 +3062,22 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -3103,7 +3110,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -3112,18 +3119,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c t="s" r="M40" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -3138,27 +3145,27 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c t="s" r="M41" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -3173,7 +3180,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -3182,13 +3189,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -3206,22 +3213,22 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3254,7 +3261,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3263,18 +3270,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -3289,27 +3296,27 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3324,7 +3331,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3333,13 +3340,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3357,13 +3364,13 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>16</v>
@@ -3535,7 +3542,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G54" s="8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c t="s" r="H54" s="8">
         <v>128</v>
@@ -3611,10 +3618,10 @@
         <v>128</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3686,7 +3693,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>17</v>
@@ -3727,7 +3734,7 @@
         <v>141</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J60" s="7">
         <v>142</v>
@@ -3760,10 +3767,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3811,7 +3818,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3843,7 +3850,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J64" s="7">
         <v>147</v>
@@ -3875,10 +3882,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>149</v>
@@ -3907,13 +3914,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>32</v>
@@ -3943,7 +3950,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I67" s="7">
         <v>151</v>
@@ -3973,16 +3980,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -4015,7 +4022,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -4125,7 +4132,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="I73" s="7">
         <v>151</v>
@@ -4155,7 +4162,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>17</v>
@@ -4274,7 +4281,7 @@
         <v>128</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>168</v>
@@ -4306,7 +4313,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>128</v>
@@ -4390,7 +4397,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I82" s="7">
         <v>174</v>
@@ -4422,13 +4429,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>176</v>
@@ -4460,13 +4467,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="I84" s="7">
         <v>139</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4492,7 +4499,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>17</v>
@@ -4530,7 +4537,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I86" s="7">
         <v>32</v>
@@ -4560,13 +4567,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>181</v>
@@ -4596,13 +4603,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I88" s="7">
         <v>152</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4626,7 +4633,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>17</v>
@@ -4688,7 +4695,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4718,7 +4725,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4748,7 +4755,7 @@
         <v>144</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>35</v>
@@ -4791,7 +4798,7 @@
         <v>189</v>
       </c>
       <c t="s" r="K94" s="7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
@@ -4831,13 +4838,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>157</v>
@@ -4869,13 +4876,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4899,13 +4906,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
+        <v>72</v>
+      </c>
+      <c t="s" r="H98" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I98" s="7">
         <v>58</v>
-      </c>
-      <c t="s" r="H98" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I98" s="7">
-        <v>46</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>153</v>
@@ -4935,7 +4942,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c t="s" r="I99" s="7">
         <v>193</v>
@@ -4986,7 +4993,7 @@
         <v>195</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>149</v>
@@ -5021,7 +5028,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>197</v>
@@ -5203,7 +5210,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>207</v>
@@ -5241,7 +5248,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5303,7 +5310,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>136</v>
@@ -5333,7 +5340,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>17</v>
@@ -5458,7 +5465,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5490,7 +5497,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>220</v>
@@ -5526,7 +5533,7 @@
         <v>221</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5568,13 +5575,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c t="s" r="I120" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5600,13 +5607,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>199</v>
@@ -5717,7 +5724,7 @@
         <v>156</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I125" s="7">
         <v>228</v>
@@ -5726,7 +5733,7 @@
         <v>229</v>
       </c>
       <c t="s" r="K125" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
@@ -5751,7 +5758,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>144</v>
@@ -5763,7 +5770,7 @@
         <v>42</v>
       </c>
       <c t="s" r="K126" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
@@ -5791,7 +5798,7 @@
         <v>144</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I127" s="7">
         <v>232</v>
@@ -5800,11 +5807,11 @@
         <v>233</v>
       </c>
       <c t="s" r="K127" s="7">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5825,7 +5832,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>156</v>
@@ -5873,10 +5880,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I130" s="7">
         <v>236</v>
@@ -5908,13 +5915,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>238</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>239</v>
@@ -5944,7 +5951,7 @@
         <v>238</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I132" s="7">
         <v>240</v>
@@ -5974,10 +5981,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c t="s" r="I133" s="7">
         <v>241</v>
@@ -6031,7 +6038,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6063,10 +6070,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -6093,13 +6100,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I137" s="7">
         <v>233</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6123,7 +6130,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>16</v>
@@ -6281,7 +6288,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6351,7 +6358,7 @@
         <v>210</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6461,7 +6468,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I149" s="7">
         <v>42</v>
@@ -6481,7 +6488,7 @@
         <v>7614</v>
       </c>
       <c t="s" r="C150" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
@@ -6491,7 +6498,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>17</v>
@@ -6514,7 +6521,7 @@
         <v>7614</v>
       </c>
       <c t="s" r="C151" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
@@ -6575,7 +6582,7 @@
         <v>156</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I153" s="7">
         <v>175</v>
@@ -6609,16 +6616,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6642,16 +6649,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>265</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6675,7 +6682,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>156</v>
@@ -6713,7 +6720,7 @@
         <v>7661</v>
       </c>
       <c t="s" r="C158" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
@@ -6748,7 +6755,7 @@
         <v>7661</v>
       </c>
       <c t="s" r="C159" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
@@ -6761,7 +6768,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I159" s="7">
         <v>271</v>
@@ -6791,13 +6798,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>273</v>
@@ -6839,7 +6846,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>16</v>
@@ -6883,7 +6890,7 @@
         <v>275</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6913,7 +6920,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>276</v>
@@ -6964,7 +6971,7 @@
         <v>279</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7099,7 +7106,7 @@
         <v>288</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>159</v>
@@ -7240,7 +7247,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>128</v>
@@ -7249,7 +7256,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7278,13 +7285,13 @@
         <v>128</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>229</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7310,7 +7317,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>294</v>
@@ -7319,7 +7326,7 @@
         <v>295</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7348,7 +7355,7 @@
         <v>294</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>297</v>
@@ -7378,7 +7385,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>294</v>
@@ -7414,7 +7421,7 @@
         <v>294</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I180" s="7">
         <v>298</v>
@@ -7500,7 +7507,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>303</v>
@@ -7508,7 +7515,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7532,7 +7539,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>121</v>
@@ -7542,7 +7549,9 @@
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
-      <c r="M184" s="7"/>
+      <c t="s" r="M184" s="7">
+        <v>170</v>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c r="A185" s="6"/>
@@ -7577,13 +7586,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>270</v>
@@ -7656,7 +7665,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7686,7 +7695,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>309</v>
@@ -7804,7 +7813,7 @@
         <v>311</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>295</v>
@@ -7842,7 +7851,7 @@
         <v>285</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7902,13 +7911,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>199</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7932,7 +7941,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>16</v>
@@ -8054,7 +8063,7 @@
         <v>144</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>230</v>
@@ -8160,7 +8169,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8202,10 +8211,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>176</v>
@@ -8213,7 +8222,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8234,7 +8243,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>17</v>
@@ -8278,7 +8287,7 @@
         <v>325</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8310,7 +8319,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>125</v>
@@ -8495,7 +8504,7 @@
         <v>307</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8524,13 +8533,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>330</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8554,13 +8563,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>124</v>
@@ -8590,7 +8599,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>331</v>
@@ -8620,7 +8629,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
@@ -8677,7 +8686,7 @@
         <v>334</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8706,13 +8715,13 @@
         <v>311</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I222" s="7">
         <v>336</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8738,7 +8747,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>16</v>
@@ -8812,7 +8821,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>171</v>
@@ -8842,7 +8851,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="I226" s="7">
         <v>186</v>
@@ -8872,7 +8881,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>16</v>
@@ -8996,7 +9005,7 @@
         <v>144</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>134</v>
@@ -9029,10 +9038,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -9062,7 +9071,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>115</v>
@@ -9140,10 +9149,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>349</v>
@@ -9172,7 +9181,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>17</v>
@@ -9181,7 +9190,7 @@
         <v>295</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9246,7 +9255,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>353</v>
@@ -9324,7 +9333,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>147</v>
@@ -9335,7 +9344,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9356,7 +9365,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
@@ -9365,7 +9374,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9400,7 +9409,7 @@
         <v>233</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9430,7 +9439,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>239</v>
@@ -9463,7 +9472,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>357</v>
@@ -9508,7 +9517,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>145</v>
@@ -9540,7 +9549,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>16</v>
@@ -9554,7 +9563,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9584,7 +9593,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9616,7 +9625,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>364</v>
@@ -9649,7 +9658,7 @@
         <v>250</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>186</v>
@@ -9712,7 +9721,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>365</v>
@@ -9863,7 +9872,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>142</v>
@@ -9893,7 +9902,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>17</v>
@@ -9947,7 +9956,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>341</v>
@@ -9955,7 +9964,7 @@
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10045,7 +10054,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>154</v>
@@ -10090,13 +10099,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>352</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>374</v>
@@ -10128,7 +10137,7 @@
         <v>352</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>133</v>
@@ -10160,7 +10169,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>128</v>
@@ -10196,10 +10205,10 @@
         <v>128</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>124</v>
@@ -10226,13 +10235,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>115</v>
@@ -10283,7 +10292,7 @@
         <v>273</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c t="s" r="K273" s="7">
         <v>168</v>
@@ -10320,14 +10329,14 @@
         <v>263</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c t="s" r="K274" s="7">
         <v>281</v>
       </c>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10420,10 +10429,10 @@
         <v>311</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10483,7 +10492,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>115</v>
@@ -10513,7 +10522,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>16</v>
@@ -10637,7 +10646,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>170</v>
@@ -10783,7 +10792,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>175</v>
@@ -10815,7 +10824,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>17</v>
@@ -10889,7 +10898,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>171</v>
@@ -10919,13 +10928,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10949,7 +10958,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>17</v>
@@ -10997,13 +11006,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>121</v>
@@ -11038,7 +11047,7 @@
         <v>391</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>193</v>
@@ -11196,10 +11205,10 @@
         <v>349</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="K302" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
@@ -11267,7 +11276,7 @@
         <v>311</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>239</v>
@@ -11303,7 +11312,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11342,7 +11351,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>16</v>
@@ -11380,7 +11389,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>240</v>
@@ -11504,7 +11513,7 @@
         <v>406</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11564,7 +11573,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>407</v>
@@ -11594,16 +11603,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11651,7 +11660,7 @@
         <v>410</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11683,7 +11692,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>341</v>
@@ -11691,7 +11700,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11831,7 +11840,7 @@
         <v>195</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>284</v>
@@ -11863,13 +11872,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>341</v>
@@ -11965,7 +11974,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>416</v>
@@ -11995,7 +12004,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>16</v>
@@ -12122,7 +12131,7 @@
         <v>330</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12260,7 +12269,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>16</v>
@@ -12301,7 +12310,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>338</v>
@@ -12339,7 +12348,7 @@
         <v>270</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12371,10 +12380,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12482,10 +12491,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>176</v>
@@ -12514,13 +12523,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>144</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>118</v>
@@ -12552,10 +12561,10 @@
         <v>144</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>43</v>
@@ -12584,16 +12593,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>232</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12617,10 +12626,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>275</v>
@@ -12741,7 +12750,7 @@
         <v>144</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>378</v>
@@ -12771,7 +12780,7 @@
         <v>144</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>364</v>
@@ -12801,7 +12810,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>144</v>
@@ -12955,7 +12964,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>176</v>
@@ -12987,13 +12996,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>133</v>
@@ -13035,7 +13044,9 @@
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
+      <c t="s" r="M361" s="7">
+        <v>271</v>
+      </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
       <c t="s" r="A362" s="6">
@@ -13091,10 +13102,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>152</v>
@@ -13121,7 +13132,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>16</v>
@@ -13218,7 +13229,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13389,7 +13400,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>18</v>
@@ -13421,7 +13432,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>311</v>
@@ -13465,7 +13476,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13497,7 +13508,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>140</v>
@@ -13565,7 +13576,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>171</v>
@@ -13754,7 +13765,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13786,7 +13797,7 @@
         <v>437</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>142</v>
@@ -13819,7 +13830,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>160</v>
@@ -13849,7 +13860,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>240</v>
@@ -13879,7 +13890,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>16</v>
@@ -13930,13 +13941,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="K390" s="7">
         <v>147</v>
@@ -13964,7 +13975,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
@@ -14010,7 +14021,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14043,7 +14054,7 @@
         <v>322</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14106,7 +14117,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>18</v>
@@ -14222,7 +14233,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>411</v>
@@ -14252,7 +14263,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>171</v>
@@ -14303,7 +14314,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>32</v>
@@ -14416,7 +14427,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>466</v>
@@ -14448,7 +14459,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>17</v>
@@ -14536,7 +14547,7 @@
       </c>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>109</v>
+        <v>75</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14563,7 +14574,7 @@
         <v>381</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>265</v>
@@ -14713,7 +14724,7 @@
         <v>229</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14745,10 +14756,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14853,7 +14864,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>195</v>
@@ -14862,7 +14873,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14895,7 +14906,7 @@
         <v>315</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14957,7 +14968,7 @@
         <v>8520</v>
       </c>
       <c t="s" r="C424" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
@@ -14967,13 +14978,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>364</v>
@@ -14992,7 +15003,7 @@
         <v>8521</v>
       </c>
       <c t="s" r="C425" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
@@ -15002,16 +15013,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="H425" s="8">
+        <v>59</v>
+      </c>
+      <c t="s" r="I425" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="J425" s="7">
         <v>47</v>
-      </c>
-      <c t="s" r="I425" s="7">
-        <v>45</v>
-      </c>
-      <c t="s" r="J425" s="7">
-        <v>74</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -15025,7 +15036,7 @@
         <v>8020</v>
       </c>
       <c t="s" r="C426" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
@@ -15035,7 +15046,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>201</v>
@@ -15058,7 +15069,7 @@
         <v>8021</v>
       </c>
       <c t="s" r="C427" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
@@ -15071,7 +15082,7 @@
         <v>201</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I427" s="7">
         <v>477</v>
@@ -15119,7 +15130,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>228</v>
@@ -15151,16 +15162,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -15189,7 +15200,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="I431" s="7">
         <v>295</v>
@@ -15221,7 +15232,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>17</v>
@@ -15230,7 +15241,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -15260,7 +15271,7 @@
         <v>481</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>124</v>
@@ -15296,7 +15307,7 @@
         <v>239</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15442,7 +15453,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>242</v>
@@ -15474,13 +15485,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15506,7 +15517,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>17</v>
@@ -15519,7 +15530,9 @@
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
-      <c r="M441" s="7"/>
+      <c t="s" r="M441" s="7">
+        <v>486</v>
+      </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
       <c t="s" r="A442" s="6">
@@ -15542,7 +15555,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="I442" s="7">
         <v>134</v>
@@ -15572,13 +15585,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>415</v>
@@ -15644,10 +15657,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15680,7 +15693,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15695,12 +15708,12 @@
         <v>303</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15715,7 +15728,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15727,10 +15740,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15748,7 +15761,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15757,7 +15770,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c t="s" r="I449" s="7">
         <v>22</v>
@@ -15781,13 +15794,13 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>16</v>
@@ -15829,7 +15842,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F452" s="7">
         <v>321</v>
@@ -15844,12 +15857,12 @@
         <v>267</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -15864,7 +15877,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
@@ -15876,7 +15889,7 @@
         <v>362</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c t="s" r="J453" s="7">
         <v>43</v>
@@ -15884,7 +15897,7 @@
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -15899,7 +15912,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F454" s="7">
         <v>321</v>
@@ -15934,7 +15947,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F455" s="7">
         <v>321</v>
@@ -15943,7 +15956,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I455" s="7">
         <v>151</v>
@@ -15971,13 +15984,13 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F456" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>17</v>
@@ -16004,7 +16017,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -16013,7 +16026,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I457" s="7">
         <v>322</v>
@@ -16056,7 +16069,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -16076,7 +16089,7 @@
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16091,7 +16104,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F460" s="7">
         <v>320</v>
@@ -16100,7 +16113,7 @@
         <v>352</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="I460" s="7">
         <v>33</v>
@@ -16124,19 +16137,19 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F461" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>352</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c t="s" r="J461" s="7">
         <v>416</v>
@@ -16157,7 +16170,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F462" s="7">
         <v>320</v>
@@ -16205,16 +16218,16 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H464" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I464" s="7">
         <v>242</v>
@@ -16240,19 +16253,19 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>415</v>
@@ -16260,7 +16273,7 @@
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -16275,16 +16288,16 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I466" s="7">
         <v>137</v>
@@ -16323,13 +16336,13 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G468" s="8">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c t="s" r="H468" s="8">
         <v>16</v>
@@ -16358,7 +16371,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -16367,7 +16380,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c t="s" r="I469" s="7">
         <v>331</v>
@@ -16406,22 +16419,22 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H471" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I471" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -16441,22 +16454,22 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G472" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c t="s" r="I472" s="7">
         <v>158</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -16474,22 +16487,22 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c t="s" r="H473" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I473" s="7">
         <v>346</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16515,36 +16528,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B475" s="7">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c t="s" r="C475" s="7">
         <v>14</v>
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F475" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G475" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c t="s" r="H475" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J475" s="7">
         <v>396</v>
       </c>
       <c t="s" r="K475" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L475" s="7"/>
       <c t="s" r="M475" s="7">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="476" ht="14.25" customHeight="1">
@@ -16559,7 +16572,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F476" s="7">
         <v>330</v>
@@ -16568,7 +16581,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H476" s="8">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c t="s" r="I476" s="7">
         <v>130</v>
@@ -16594,19 +16607,19 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F477" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G477" s="8">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c t="s" r="H477" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J477" s="7">
         <v>215</v>
@@ -16642,19 +16655,19 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G479" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J479" s="7">
         <v>134</v>
@@ -16662,7 +16675,7 @@
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -16677,22 +16690,22 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F480" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G480" s="8">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c t="s" r="H480" s="8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="I480" s="7">
         <v>315</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16725,7 +16738,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
@@ -16734,18 +16747,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H482" s="8">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c t="s" r="I482" s="7">
         <v>281</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -16760,19 +16773,19 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F483" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G483" s="8">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c t="s" r="H483" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I483" s="7">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c t="s" r="J483" s="7">
         <v>18</v>
@@ -16783,7 +16796,7 @@
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c t="s" r="A484" s="9">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B484" s="9"/>
       <c r="C484" s="9"/>
@@ -16803,7 +16816,7 @@
     <row r="485" ht="66" customHeight="1"/>
     <row r="486" ht="16.5" customHeight="1">
       <c t="s" r="A486" s="10">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B486" s="10"/>
       <c r="C486" s="10"/>
@@ -16816,7 +16829,7 @@
       <c r="J486" s="10"/>
       <c r="K486" s="10"/>
       <c t="s" r="L486" s="11">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M486" s="11"/>
       <c r="N486" s="11"/>
